--- a/data/synthetic-study/SPbE-2026_dataset.xlsx
+++ b/data/synthetic-study/SPbE-2026_dataset.xlsx
@@ -431,25 +431,25 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,52 +460,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>enrollment_date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>age_years</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sex</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>study_arm</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>bmi_kg_m2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>baseline_glucose_mg_dl</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>week12_glucose_mg_dl</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>baseline_hba1c_pct</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>week12_hba1c_pct</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>baseline_weight_kg</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>week12_weight_kg</t>
+          <t>hba1c_pct</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -515,22 +515,22 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>diastolic_bp_mmhg</t>
+          <t>on_glucose_medication</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ldl_mg_dl</t>
+          <t>adverse_event</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>hdl_mg_dl</t>
+          <t>completed_study</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>triglycerides_mg_dl</t>
+          <t>visit_date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -540,17 +540,17 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>adverse_event</t>
+          <t>investigator_orcid</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>withdrew</t>
+          <t>reference_pmid</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>collection_date</t>
+          <t>protocol_doi</t>
         </is>
       </c>
     </row>
@@ -560,71 +560,69 @@
           <t>SUBJ-001</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>60</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G2" t="n">
-        <v>109</v>
-      </c>
       <c r="H2" t="n">
-        <v>5.9</v>
+        <v>31.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>90.59999999999999</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>125</v>
-      </c>
-      <c r="M2" t="n">
-        <v>71</v>
-      </c>
-      <c r="N2" t="n">
-        <v>91</v>
-      </c>
-      <c r="O2" t="n">
-        <v>40</v>
-      </c>
-      <c r="P2" t="n">
-        <v>117</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>72</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -634,71 +632,79 @@
           <t>SUBJ-002</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>53</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>46</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>29.6</v>
       </c>
-      <c r="F3" t="n">
-        <v>110</v>
-      </c>
-      <c r="G3" t="n">
-        <v>104</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="J3" t="n">
-        <v>84.7</v>
+        <v>95</v>
       </c>
       <c r="K3" t="n">
-        <v>82.09999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="L3" t="n">
-        <v>136</v>
-      </c>
-      <c r="M3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N3" t="n">
-        <v>96</v>
-      </c>
-      <c r="O3" t="n">
-        <v>40</v>
-      </c>
-      <c r="P3" t="n">
-        <v>138</v>
+        <v>112</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -708,71 +714,79 @@
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>65</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>51</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>119</v>
-      </c>
-      <c r="G4" t="n">
-        <v>120</v>
-      </c>
       <c r="H4" t="n">
-        <v>6.4</v>
+        <v>32.5</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>108</v>
       </c>
       <c r="J4" t="n">
-        <v>88.59999999999999</v>
+        <v>105</v>
       </c>
       <c r="K4" t="n">
-        <v>87.09999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="L4" t="n">
-        <v>123</v>
-      </c>
-      <c r="M4" t="n">
-        <v>88</v>
-      </c>
-      <c r="N4" t="n">
-        <v>102</v>
-      </c>
-      <c r="O4" t="n">
-        <v>60</v>
-      </c>
-      <c r="P4" t="n">
-        <v>98</v>
+        <v>129</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -782,71 +796,79 @@
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>47</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>46</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>29</v>
-      </c>
-      <c r="F5" t="n">
-        <v>116</v>
-      </c>
-      <c r="G5" t="n">
-        <v>100</v>
-      </c>
       <c r="H5" t="n">
-        <v>6.3</v>
+        <v>31.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6.1</v>
+        <v>122</v>
       </c>
       <c r="J5" t="n">
-        <v>82.7</v>
+        <v>107</v>
       </c>
       <c r="K5" t="n">
-        <v>78.5</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
-        <v>133</v>
-      </c>
-      <c r="M5" t="n">
-        <v>72</v>
-      </c>
-      <c r="N5" t="n">
-        <v>128</v>
-      </c>
-      <c r="O5" t="n">
-        <v>58</v>
-      </c>
-      <c r="P5" t="n">
-        <v>111</v>
+        <v>114</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="Q5" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -856,71 +878,79 @@
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>52</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I6" t="n">
         <v>122</v>
       </c>
-      <c r="G6" t="n">
-        <v>116</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.9</v>
-      </c>
       <c r="J6" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="K6" t="n">
-        <v>95.8</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>137</v>
-      </c>
-      <c r="M6" t="n">
-        <v>80</v>
-      </c>
-      <c r="N6" t="n">
-        <v>115</v>
-      </c>
-      <c r="O6" t="n">
-        <v>46</v>
-      </c>
-      <c r="P6" t="n">
-        <v>98</v>
+        <v>135</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -930,71 +960,79 @@
           <t>SUBJ-006</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>52</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>47</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>106</v>
-      </c>
-      <c r="G7" t="n">
-        <v>97</v>
-      </c>
       <c r="H7" t="n">
-        <v>6.2</v>
+        <v>29.2</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>122</v>
       </c>
       <c r="J7" t="n">
-        <v>94.40000000000001</v>
+        <v>108</v>
       </c>
       <c r="K7" t="n">
-        <v>91.2</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
-        <v>123</v>
-      </c>
-      <c r="M7" t="n">
-        <v>77</v>
-      </c>
-      <c r="N7" t="n">
-        <v>98</v>
-      </c>
-      <c r="O7" t="n">
-        <v>54</v>
-      </c>
-      <c r="P7" t="n">
-        <v>153</v>
+        <v>130</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1004,71 +1042,79 @@
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>60</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>63</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>115</v>
-      </c>
-      <c r="G8" t="n">
-        <v>116</v>
-      </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>33.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>122</v>
       </c>
       <c r="J8" t="n">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="K8" t="n">
-        <v>86.2</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
-        <v>112</v>
-      </c>
-      <c r="M8" t="n">
-        <v>73</v>
-      </c>
-      <c r="N8" t="n">
-        <v>133</v>
-      </c>
-      <c r="O8" t="n">
-        <v>55</v>
-      </c>
-      <c r="P8" t="n">
-        <v>186</v>
+        <v>119</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
       </c>
       <c r="Q8" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1078,71 +1124,79 @@
           <t>SUBJ-008</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>53</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>42</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>110</v>
-      </c>
-      <c r="G9" t="n">
-        <v>96</v>
-      </c>
       <c r="H9" t="n">
-        <v>6.2</v>
+        <v>30.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>105</v>
       </c>
       <c r="J9" t="n">
-        <v>75.2</v>
+        <v>97</v>
       </c>
       <c r="K9" t="n">
-        <v>71.2</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>128</v>
-      </c>
-      <c r="M9" t="n">
-        <v>76</v>
-      </c>
-      <c r="N9" t="n">
-        <v>99</v>
-      </c>
-      <c r="O9" t="n">
-        <v>49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>187</v>
+        <v>120</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
       </c>
       <c r="Q9" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1152,71 +1206,79 @@
           <t>SUBJ-009</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>40</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>54</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>111</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I10" t="n">
         <v>110</v>
       </c>
-      <c r="H10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="J10" t="n">
-        <v>100.4</v>
+        <v>107</v>
       </c>
       <c r="K10" t="n">
-        <v>101.1</v>
+        <v>6.1</v>
       </c>
       <c r="L10" t="n">
-        <v>114</v>
-      </c>
-      <c r="M10" t="n">
-        <v>87</v>
-      </c>
-      <c r="N10" t="n">
-        <v>139</v>
-      </c>
-      <c r="O10" t="n">
-        <v>42</v>
-      </c>
-      <c r="P10" t="n">
-        <v>106</v>
+        <v>128</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
       </c>
       <c r="Q10" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1226,71 +1288,79 @@
           <t>SUBJ-010</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>59</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>64</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="F11" t="n">
-        <v>119</v>
-      </c>
-      <c r="G11" t="n">
-        <v>110</v>
-      </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>29.9</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>108</v>
       </c>
       <c r="J11" t="n">
-        <v>92.2</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>89.2</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>126</v>
-      </c>
-      <c r="M11" t="n">
-        <v>73</v>
-      </c>
-      <c r="N11" t="n">
-        <v>105</v>
-      </c>
-      <c r="O11" t="n">
-        <v>45</v>
-      </c>
-      <c r="P11" t="n">
-        <v>98</v>
+        <v>123</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
       </c>
       <c r="Q11" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1300,71 +1370,79 @@
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>47</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F12" t="n">
-        <v>122</v>
-      </c>
-      <c r="G12" t="n">
-        <v>124</v>
-      </c>
       <c r="H12" t="n">
-        <v>5.9</v>
+        <v>31.3</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>104</v>
       </c>
       <c r="J12" t="n">
-        <v>97.8</v>
+        <v>105</v>
       </c>
       <c r="K12" t="n">
-        <v>98.59999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="L12" t="n">
-        <v>133</v>
-      </c>
-      <c r="M12" t="n">
-        <v>85</v>
-      </c>
-      <c r="N12" t="n">
-        <v>103</v>
-      </c>
-      <c r="O12" t="n">
-        <v>55</v>
-      </c>
-      <c r="P12" t="n">
-        <v>106</v>
+        <v>117</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
       </c>
       <c r="Q12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1374,71 +1452,79 @@
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>65</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>105</v>
-      </c>
-      <c r="G13" t="n">
-        <v>89</v>
-      </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>33.2</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>124</v>
       </c>
       <c r="J13" t="n">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="K13" t="n">
-        <v>81.59999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
-        <v>132</v>
-      </c>
-      <c r="M13" t="n">
-        <v>73</v>
-      </c>
-      <c r="N13" t="n">
-        <v>93</v>
-      </c>
-      <c r="O13" t="n">
-        <v>50</v>
-      </c>
-      <c r="P13" t="n">
-        <v>183</v>
+        <v>119</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="Q13" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1448,71 +1534,79 @@
           <t>SUBJ-013</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>46</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>62</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>107</v>
-      </c>
-      <c r="G14" t="n">
-        <v>105</v>
-      </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>26.5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>119</v>
       </c>
       <c r="J14" t="n">
-        <v>74.3</v>
+        <v>118</v>
       </c>
       <c r="K14" t="n">
-        <v>72.90000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>115</v>
-      </c>
-      <c r="M14" t="n">
-        <v>71</v>
-      </c>
-      <c r="N14" t="n">
-        <v>131</v>
-      </c>
-      <c r="O14" t="n">
-        <v>55</v>
-      </c>
-      <c r="P14" t="n">
-        <v>197</v>
+        <v>122</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
       </c>
       <c r="Q14" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1522,71 +1616,79 @@
           <t>SUBJ-014</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>53</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>114</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I15" t="n">
         <v>108</v>
       </c>
-      <c r="H15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5.7</v>
-      </c>
       <c r="J15" t="n">
-        <v>83.7</v>
+        <v>94</v>
       </c>
       <c r="K15" t="n">
-        <v>78.5</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>121</v>
-      </c>
-      <c r="M15" t="n">
-        <v>83</v>
-      </c>
-      <c r="N15" t="n">
-        <v>134</v>
-      </c>
-      <c r="O15" t="n">
-        <v>55</v>
-      </c>
-      <c r="P15" t="n">
-        <v>174</v>
+        <v>125</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
       </c>
       <c r="Q15" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1596,71 +1698,69 @@
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>46</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>47</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>119</v>
-      </c>
-      <c r="G16" t="n">
-        <v>121</v>
-      </c>
       <c r="H16" t="n">
-        <v>6.2</v>
+        <v>30.3</v>
       </c>
       <c r="I16" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>89</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>117</v>
-      </c>
-      <c r="M16" t="n">
-        <v>71</v>
-      </c>
-      <c r="N16" t="n">
-        <v>122</v>
-      </c>
-      <c r="O16" t="n">
-        <v>40</v>
-      </c>
-      <c r="P16" t="n">
-        <v>198</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>69</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1670,71 +1770,79 @@
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>52</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>65</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>120</v>
-      </c>
-      <c r="G17" t="n">
-        <v>111</v>
-      </c>
       <c r="H17" t="n">
-        <v>6.1</v>
+        <v>31.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="J17" t="n">
-        <v>74.5</v>
+        <v>107</v>
       </c>
       <c r="K17" t="n">
-        <v>70.40000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
-        <v>122</v>
-      </c>
-      <c r="M17" t="n">
-        <v>78</v>
-      </c>
-      <c r="N17" t="n">
-        <v>103</v>
-      </c>
-      <c r="O17" t="n">
-        <v>59</v>
-      </c>
-      <c r="P17" t="n">
-        <v>181</v>
+        <v>112</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1744,71 +1852,79 @@
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>44</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>52</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>104</v>
-      </c>
-      <c r="G18" t="n">
-        <v>106</v>
-      </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>28.1</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>117</v>
       </c>
       <c r="J18" t="n">
-        <v>101.9</v>
+        <v>116</v>
       </c>
       <c r="K18" t="n">
-        <v>102.7</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
-      </c>
-      <c r="M18" t="n">
-        <v>74</v>
-      </c>
-      <c r="N18" t="n">
-        <v>149</v>
-      </c>
-      <c r="O18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P18" t="n">
-        <v>202</v>
+        <v>126</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
       </c>
       <c r="Q18" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1818,71 +1934,79 @@
           <t>SUBJ-018</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>45</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>41</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="F19" t="n">
-        <v>124</v>
-      </c>
-      <c r="G19" t="n">
-        <v>114</v>
-      </c>
       <c r="H19" t="n">
-        <v>6.1</v>
+        <v>26.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>123</v>
       </c>
       <c r="J19" t="n">
-        <v>91.59999999999999</v>
+        <v>110</v>
       </c>
       <c r="K19" t="n">
-        <v>90.09999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="L19" t="n">
-        <v>121</v>
-      </c>
-      <c r="M19" t="n">
-        <v>73</v>
-      </c>
-      <c r="N19" t="n">
-        <v>150</v>
-      </c>
-      <c r="O19" t="n">
-        <v>42</v>
-      </c>
-      <c r="P19" t="n">
-        <v>123</v>
+        <v>128</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
       </c>
       <c r="Q19" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1892,71 +2016,79 @@
           <t>SUBJ-019</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>49</v>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>43</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F20" t="n">
-        <v>108</v>
-      </c>
-      <c r="G20" t="n">
-        <v>106</v>
-      </c>
       <c r="H20" t="n">
-        <v>6.1</v>
+        <v>31</v>
       </c>
       <c r="I20" t="n">
-        <v>6.1</v>
+        <v>104</v>
       </c>
       <c r="J20" t="n">
-        <v>99.2</v>
+        <v>105</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>5.8</v>
       </c>
       <c r="L20" t="n">
-        <v>138</v>
-      </c>
-      <c r="M20" t="n">
-        <v>78</v>
-      </c>
-      <c r="N20" t="n">
-        <v>92</v>
-      </c>
-      <c r="O20" t="n">
-        <v>38</v>
-      </c>
-      <c r="P20" t="n">
-        <v>132</v>
+        <v>130</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -1966,71 +2098,79 @@
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>57</v>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>60</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>105</v>
-      </c>
-      <c r="G21" t="n">
-        <v>98</v>
-      </c>
       <c r="H21" t="n">
-        <v>6.4</v>
+        <v>28.5</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="J21" t="n">
-        <v>76.5</v>
+        <v>103</v>
       </c>
       <c r="K21" t="n">
-        <v>74.90000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="L21" t="n">
-        <v>129</v>
-      </c>
-      <c r="M21" t="n">
-        <v>74</v>
-      </c>
-      <c r="N21" t="n">
-        <v>117</v>
-      </c>
-      <c r="O21" t="n">
-        <v>42</v>
-      </c>
-      <c r="P21" t="n">
-        <v>95</v>
+        <v>114</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2040,71 +2180,79 @@
           <t>SUBJ-021</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>46</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>51</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>113</v>
-      </c>
-      <c r="G22" t="n">
-        <v>107</v>
-      </c>
       <c r="H22" t="n">
-        <v>6.3</v>
+        <v>29</v>
       </c>
       <c r="I22" t="n">
-        <v>6.3</v>
+        <v>104</v>
       </c>
       <c r="J22" t="n">
-        <v>90.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="K22" t="n">
-        <v>91.09999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="L22" t="n">
-        <v>117</v>
-      </c>
-      <c r="M22" t="n">
-        <v>75</v>
-      </c>
-      <c r="N22" t="n">
-        <v>146</v>
-      </c>
-      <c r="O22" t="n">
-        <v>51</v>
-      </c>
-      <c r="P22" t="n">
-        <v>93</v>
+        <v>138</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
       </c>
       <c r="Q22" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2114,71 +2262,79 @@
           <t>SUBJ-022</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>48</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>43</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>105</v>
-      </c>
-      <c r="G23" t="n">
-        <v>93</v>
-      </c>
       <c r="H23" t="n">
-        <v>6.3</v>
+        <v>28.2</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>111</v>
       </c>
       <c r="J23" t="n">
-        <v>78.7</v>
+        <v>95</v>
       </c>
       <c r="K23" t="n">
-        <v>73.90000000000001</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>121</v>
-      </c>
-      <c r="M23" t="n">
-        <v>77</v>
-      </c>
-      <c r="N23" t="n">
-        <v>104</v>
-      </c>
-      <c r="O23" t="n">
-        <v>38</v>
-      </c>
-      <c r="P23" t="n">
-        <v>174</v>
+        <v>134</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2188,71 +2344,79 @@
           <t>SUBJ-023</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>42</v>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I24" t="n">
         <v>118</v>
       </c>
-      <c r="G24" t="n">
-        <v>114</v>
-      </c>
-      <c r="H24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
       <c r="J24" t="n">
-        <v>81.90000000000001</v>
+        <v>113</v>
       </c>
       <c r="K24" t="n">
-        <v>82.8</v>
+        <v>5.7</v>
       </c>
       <c r="L24" t="n">
-        <v>120</v>
-      </c>
-      <c r="M24" t="n">
-        <v>75</v>
-      </c>
-      <c r="N24" t="n">
-        <v>127</v>
-      </c>
-      <c r="O24" t="n">
-        <v>46</v>
-      </c>
-      <c r="P24" t="n">
-        <v>94</v>
+        <v>116</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2262,71 +2426,69 @@
           <t>SUBJ-024</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>53</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>44</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>120</v>
-      </c>
-      <c r="G25" t="n">
-        <v>111</v>
-      </c>
       <c r="H25" t="n">
-        <v>5.9</v>
+        <v>30.7</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="K25" t="n">
-        <v>66.90000000000001</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>135</v>
-      </c>
-      <c r="M25" t="n">
-        <v>76</v>
-      </c>
-      <c r="N25" t="n">
-        <v>113</v>
-      </c>
-      <c r="O25" t="n">
-        <v>51</v>
-      </c>
-      <c r="P25" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>79</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2336,71 +2498,79 @@
           <t>SUBJ-025</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>56</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>46</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>112</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>111</v>
+      </c>
+      <c r="J26" t="n">
         <v>108</v>
       </c>
-      <c r="H26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>77.8</v>
-      </c>
       <c r="K26" t="n">
-        <v>76.8</v>
+        <v>5.9</v>
       </c>
       <c r="L26" t="n">
-        <v>135</v>
-      </c>
-      <c r="M26" t="n">
-        <v>75</v>
-      </c>
-      <c r="N26" t="n">
-        <v>129</v>
-      </c>
-      <c r="O26" t="n">
-        <v>56</v>
-      </c>
-      <c r="P26" t="n">
-        <v>128</v>
+        <v>125</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
       </c>
       <c r="Q26" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2410,71 +2580,79 @@
           <t>SUBJ-026</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>46</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>65</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="F27" t="n">
-        <v>121</v>
-      </c>
-      <c r="G27" t="n">
-        <v>105</v>
-      </c>
       <c r="H27" t="n">
-        <v>5.9</v>
+        <v>27.3</v>
       </c>
       <c r="I27" t="n">
-        <v>5.6</v>
+        <v>115</v>
       </c>
       <c r="J27" t="n">
-        <v>92.3</v>
+        <v>109</v>
       </c>
       <c r="K27" t="n">
-        <v>88.8</v>
+        <v>6.1</v>
       </c>
       <c r="L27" t="n">
-        <v>137</v>
-      </c>
-      <c r="M27" t="n">
-        <v>75</v>
-      </c>
-      <c r="N27" t="n">
-        <v>132</v>
-      </c>
-      <c r="O27" t="n">
-        <v>40</v>
-      </c>
-      <c r="P27" t="n">
-        <v>126</v>
+        <v>124</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="Q27" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2484,71 +2662,79 @@
           <t>SUBJ-027</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>61</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>40</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="F28" t="n">
-        <v>108</v>
-      </c>
-      <c r="G28" t="n">
-        <v>108</v>
-      </c>
       <c r="H28" t="n">
-        <v>5.7</v>
+        <v>28.6</v>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>113</v>
       </c>
       <c r="J28" t="n">
-        <v>86.3</v>
+        <v>111</v>
       </c>
       <c r="K28" t="n">
-        <v>84.8</v>
+        <v>6.3</v>
       </c>
       <c r="L28" t="n">
-        <v>125</v>
-      </c>
-      <c r="M28" t="n">
-        <v>88</v>
-      </c>
-      <c r="N28" t="n">
-        <v>102</v>
-      </c>
-      <c r="O28" t="n">
-        <v>60</v>
-      </c>
-      <c r="P28" t="n">
-        <v>179</v>
+        <v>136</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
       </c>
       <c r="Q28" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2558,71 +2744,79 @@
           <t>SUBJ-028</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>44</v>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>48</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>105</v>
-      </c>
-      <c r="G29" t="n">
-        <v>93</v>
-      </c>
       <c r="H29" t="n">
-        <v>5.9</v>
+        <v>26.3</v>
       </c>
       <c r="I29" t="n">
-        <v>5.5</v>
+        <v>123</v>
       </c>
       <c r="J29" t="n">
-        <v>92.90000000000001</v>
+        <v>109</v>
       </c>
       <c r="K29" t="n">
-        <v>89.5</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>115</v>
-      </c>
-      <c r="M29" t="n">
-        <v>84</v>
-      </c>
-      <c r="N29" t="n">
-        <v>98</v>
-      </c>
-      <c r="O29" t="n">
-        <v>52</v>
-      </c>
-      <c r="P29" t="n">
-        <v>175</v>
+        <v>123</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
       </c>
       <c r="Q29" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2632,71 +2826,79 @@
           <t>SUBJ-029</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>53</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>56</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>117</v>
-      </c>
-      <c r="G30" t="n">
-        <v>112</v>
-      </c>
       <c r="H30" t="n">
-        <v>5.9</v>
+        <v>29.5</v>
       </c>
       <c r="I30" t="n">
-        <v>5.9</v>
+        <v>114</v>
       </c>
       <c r="J30" t="n">
-        <v>91.09999999999999</v>
+        <v>113</v>
       </c>
       <c r="K30" t="n">
-        <v>89.8</v>
+        <v>6.3</v>
       </c>
       <c r="L30" t="n">
-        <v>132</v>
-      </c>
-      <c r="M30" t="n">
-        <v>77</v>
-      </c>
-      <c r="N30" t="n">
-        <v>107</v>
-      </c>
-      <c r="O30" t="n">
-        <v>52</v>
-      </c>
-      <c r="P30" t="n">
-        <v>99</v>
+        <v>122</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="Q30" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2706,71 +2908,79 @@
           <t>SUBJ-030</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>50</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>44</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>109</v>
-      </c>
-      <c r="G31" t="n">
-        <v>97</v>
-      </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>31.3</v>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>123</v>
       </c>
       <c r="J31" t="n">
-        <v>73.90000000000001</v>
+        <v>111</v>
       </c>
       <c r="K31" t="n">
-        <v>70.8</v>
+        <v>5.7</v>
       </c>
       <c r="L31" t="n">
-        <v>125</v>
-      </c>
-      <c r="M31" t="n">
-        <v>71</v>
-      </c>
-      <c r="N31" t="n">
-        <v>103</v>
-      </c>
-      <c r="O31" t="n">
-        <v>51</v>
-      </c>
-      <c r="P31" t="n">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2780,71 +2990,79 @@
           <t>SUBJ-031</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>40</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>54</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="F32" t="n">
-        <v>114</v>
-      </c>
-      <c r="G32" t="n">
-        <v>110</v>
-      </c>
       <c r="H32" t="n">
-        <v>6.1</v>
+        <v>30.1</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="J32" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="K32" t="n">
-        <v>94.3</v>
+        <v>6.2</v>
       </c>
       <c r="L32" t="n">
-        <v>120</v>
-      </c>
-      <c r="M32" t="n">
-        <v>83</v>
-      </c>
-      <c r="N32" t="n">
-        <v>121</v>
-      </c>
-      <c r="O32" t="n">
-        <v>38</v>
-      </c>
-      <c r="P32" t="n">
-        <v>139</v>
+        <v>137</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="Q32" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2854,71 +3072,79 @@
           <t>SUBJ-032</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>44</v>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>49</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F33" t="n">
-        <v>120</v>
-      </c>
-      <c r="G33" t="n">
-        <v>105</v>
-      </c>
       <c r="H33" t="n">
-        <v>6.2</v>
+        <v>27.2</v>
       </c>
       <c r="I33" t="n">
-        <v>6.1</v>
+        <v>122</v>
       </c>
       <c r="J33" t="n">
-        <v>84.90000000000001</v>
+        <v>107</v>
       </c>
       <c r="K33" t="n">
-        <v>79.90000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="L33" t="n">
-        <v>120</v>
-      </c>
-      <c r="M33" t="n">
-        <v>82</v>
-      </c>
-      <c r="N33" t="n">
-        <v>110</v>
-      </c>
-      <c r="O33" t="n">
-        <v>44</v>
-      </c>
-      <c r="P33" t="n">
-        <v>148</v>
+        <v>127</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
       </c>
       <c r="Q33" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -2928,71 +3154,79 @@
           <t>SUBJ-033</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>64</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>52</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>28</v>
-      </c>
-      <c r="F34" t="n">
-        <v>104</v>
-      </c>
-      <c r="G34" t="n">
-        <v>99</v>
-      </c>
       <c r="H34" t="n">
-        <v>5.7</v>
+        <v>31.2</v>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>120</v>
       </c>
       <c r="J34" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="K34" t="n">
-        <v>102</v>
+        <v>5.3</v>
       </c>
       <c r="L34" t="n">
         <v>136</v>
       </c>
-      <c r="M34" t="n">
-        <v>71</v>
-      </c>
-      <c r="N34" t="n">
-        <v>138</v>
-      </c>
-      <c r="O34" t="n">
-        <v>38</v>
-      </c>
-      <c r="P34" t="n">
-        <v>121</v>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="Q34" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3002,71 +3236,69 @@
           <t>SUBJ-034</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>44</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>54</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="F35" t="n">
-        <v>120</v>
-      </c>
-      <c r="G35" t="n">
-        <v>111</v>
-      </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>31.3</v>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J35" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="K35" t="n">
-        <v>79.2</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>134</v>
-      </c>
-      <c r="M35" t="n">
-        <v>73</v>
-      </c>
-      <c r="N35" t="n">
-        <v>139</v>
-      </c>
-      <c r="O35" t="n">
-        <v>43</v>
-      </c>
-      <c r="P35" t="n">
         <v>129</v>
       </c>
-      <c r="Q35" t="n">
-        <v>64</v>
-      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3076,71 +3308,79 @@
           <t>SUBJ-035</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>61</v>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>63</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>124</v>
-      </c>
-      <c r="G36" t="n">
-        <v>123</v>
-      </c>
       <c r="H36" t="n">
-        <v>5.8</v>
+        <v>28.1</v>
       </c>
       <c r="I36" t="n">
-        <v>5.7</v>
+        <v>118</v>
       </c>
       <c r="J36" t="n">
-        <v>90.8</v>
+        <v>114</v>
       </c>
       <c r="K36" t="n">
-        <v>91.5</v>
+        <v>5.6</v>
       </c>
       <c r="L36" t="n">
-        <v>133</v>
-      </c>
-      <c r="M36" t="n">
-        <v>73</v>
-      </c>
-      <c r="N36" t="n">
-        <v>140</v>
-      </c>
-      <c r="O36" t="n">
-        <v>56</v>
-      </c>
-      <c r="P36" t="n">
-        <v>190</v>
+        <v>132</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
       </c>
       <c r="Q36" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3150,71 +3390,79 @@
           <t>SUBJ-036</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>42</v>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>50</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>115</v>
-      </c>
-      <c r="G37" t="n">
-        <v>102</v>
-      </c>
       <c r="H37" t="n">
-        <v>5.8</v>
+        <v>27.1</v>
       </c>
       <c r="I37" t="n">
-        <v>5.3</v>
+        <v>116</v>
       </c>
       <c r="J37" t="n">
-        <v>91.09999999999999</v>
+        <v>109</v>
       </c>
       <c r="K37" t="n">
-        <v>86.3</v>
+        <v>5.6</v>
       </c>
       <c r="L37" t="n">
-        <v>125</v>
-      </c>
-      <c r="M37" t="n">
-        <v>75</v>
-      </c>
-      <c r="N37" t="n">
-        <v>136</v>
-      </c>
-      <c r="O37" t="n">
-        <v>54</v>
-      </c>
-      <c r="P37" t="n">
-        <v>173</v>
+        <v>134</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
       </c>
       <c r="Q37" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3224,71 +3472,79 @@
           <t>SUBJ-037</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>63</v>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>53</v>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="F38" t="n">
-        <v>109</v>
-      </c>
-      <c r="G38" t="n">
-        <v>110</v>
-      </c>
       <c r="H38" t="n">
-        <v>5.9</v>
+        <v>32.9</v>
       </c>
       <c r="I38" t="n">
-        <v>5.9</v>
+        <v>112</v>
       </c>
       <c r="J38" t="n">
-        <v>94.5</v>
+        <v>106</v>
       </c>
       <c r="K38" t="n">
-        <v>93.8</v>
+        <v>6.1</v>
       </c>
       <c r="L38" t="n">
-        <v>122</v>
-      </c>
-      <c r="M38" t="n">
-        <v>70</v>
-      </c>
-      <c r="N38" t="n">
-        <v>121</v>
-      </c>
-      <c r="O38" t="n">
-        <v>48</v>
-      </c>
-      <c r="P38" t="n">
-        <v>113</v>
+        <v>124</v>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
       </c>
       <c r="Q38" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0001-5109-3700</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3298,71 +3554,79 @@
           <t>SUBJ-038</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>50</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>47</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>33</v>
-      </c>
-      <c r="F39" t="n">
-        <v>124</v>
-      </c>
-      <c r="G39" t="n">
-        <v>114</v>
-      </c>
       <c r="H39" t="n">
-        <v>6.1</v>
+        <v>29.9</v>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>115</v>
       </c>
       <c r="J39" t="n">
-        <v>77.7</v>
+        <v>101</v>
       </c>
       <c r="K39" t="n">
-        <v>75.2</v>
+        <v>5.7</v>
       </c>
       <c r="L39" t="n">
-        <v>129</v>
-      </c>
-      <c r="M39" t="n">
-        <v>77</v>
-      </c>
-      <c r="N39" t="n">
-        <v>134</v>
-      </c>
-      <c r="O39" t="n">
-        <v>53</v>
-      </c>
-      <c r="P39" t="n">
-        <v>172</v>
+        <v>133</v>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3372,71 +3636,69 @@
           <t>SUBJ-039</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>49</v>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>58</v>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="F40" t="n">
-        <v>109</v>
-      </c>
-      <c r="G40" t="n">
-        <v>107</v>
-      </c>
       <c r="H40" t="n">
-        <v>6.2</v>
+        <v>31.1</v>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="K40" t="n">
-        <v>88.59999999999999</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>129</v>
-      </c>
-      <c r="M40" t="n">
-        <v>80</v>
-      </c>
-      <c r="N40" t="n">
-        <v>112</v>
-      </c>
-      <c r="O40" t="n">
-        <v>60</v>
-      </c>
-      <c r="P40" t="n">
-        <v>148</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>75</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" t="b">
+        <v>0</v>
+      </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3446,71 +3708,79 @@
           <t>SUBJ-040</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>43</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>50</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>TRE</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="F41" t="n">
-        <v>119</v>
-      </c>
-      <c r="G41" t="n">
-        <v>111</v>
-      </c>
       <c r="H41" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>110</v>
       </c>
       <c r="J41" t="n">
-        <v>80.3</v>
+        <v>98</v>
       </c>
       <c r="K41" t="n">
-        <v>76.40000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="L41" t="n">
-        <v>131</v>
-      </c>
-      <c r="M41" t="n">
-        <v>79</v>
-      </c>
-      <c r="N41" t="n">
-        <v>96</v>
-      </c>
-      <c r="O41" t="n">
-        <v>44</v>
-      </c>
-      <c r="P41" t="n">
-        <v>127</v>
+        <v>120</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
       </c>
       <c r="Q41" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>0000-0002-9876-5432</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>10.5281/zenodo.0000000</t>
         </is>
       </c>
     </row>
@@ -3529,11 +3799,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3544,12 +3814,12 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>field_type</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>data_type</t>
+          <t>controlled_by / authority</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -3559,7 +3829,7 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>permissible_values</t>
+          <t>example</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -3576,299 +3846,283 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Subject identifier</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>string</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUBJ-001</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>age_years</t>
+          <t>enrollment_date</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Age at enrollment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40-65</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NCIT:C25150 (Age)</t>
+          <t>ISO-8601 date</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>age_years</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biological sex</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>female | male</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NCIT:C28421 (Sex)</t>
+          <t>years</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>group</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Study arm</t>
+          <t>controlled</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>NCIT (sex)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TRE | control</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NCIT:C15538 (Treatment Arm)</t>
+          <t>NCIT:C28421 (Sex); values female=NCIT:C16576, male=NCIT:C20197</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bmi_kg_m2</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Body mass index</t>
+          <t>controlled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>kg/m^2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>GAZ / ISO-3166 branch</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NCIT:C16358 (Body Mass Index)</t>
+          <t>GAZ / ISO-3166-1 (e.g. United States = GAZ:00002459)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>baseline_glucose_mg_dl</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fasting plasma glucose, baseline</t>
+          <t>controlled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>MONDO branch</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>prediabetes</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NCIT:C105585 (Fasting Blood Glucose)</t>
+          <t>MONDO:0005827 (prediabetes)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>week12_glucose_mg_dl</t>
+          <t>study_arm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fasting plasma glucose, week 12</t>
+          <t>controlled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>NCIT (treatment arm)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NCIT:C105585 (Fasting Blood Glucose)</t>
+          <t>NCIT:C174266 (Study Arm)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>baseline_hba1c_pct</t>
+          <t>bmi_kg_m2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HbA1c, baseline</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>kg/m^2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NCIT:C64849 (Hemoglobin A1C)</t>
+          <t>NCIT:C16358 (Body Mass Index); UO:0000077 (kg/m^2)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>week12_hba1c_pct</t>
+          <t>baseline_glucose_mg_dl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HbA1c, week 12</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NCIT:C64849 (Hemoglobin A1C)</t>
+          <t>NCIT:C105585 (Fasting Blood Glucose); mg/dL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>baseline_weight_kg</t>
+          <t>week12_glucose_mg_dl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Body weight, baseline</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NCIT:C25208 (Weight)</t>
+          <t>NCIT:C105585 (Fasting Blood Glucose); mg/dL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>week12_weight_kg</t>
+          <t>hba1c_pct</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Body weight, week 12</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NCIT:C25208 (Weight)</t>
+          <t>NCIT:C64849 (Hemoglobin A1C); %</t>
         </is>
       </c>
     </row>
@@ -3880,135 +4134,107 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Systolic blood pressure, week 12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>mmHg</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NCIT:C25298 (Systolic Blood Pressure)</t>
+          <t>NCIT:C25298 (Systolic Blood Pressure); mmHg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>diastolic_bp_mmhg</t>
+          <t>on_glucose_medication</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diastolic blood pressure, week 12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NCIT:C25299 (Diastolic Blood Pressure)</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ldl_mg_dl</t>
+          <t>adverse_event</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LDL cholesterol, week 12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NCIT:C105586 (LDL Cholesterol)</t>
+          <t>NCIT:C41331 (Adverse Event)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hdl_mg_dl</t>
+          <t>completed_study</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HDL cholesterol, week 12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NCIT:C105587 (HDL Cholesterol)</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>triglycerides_mg_dl</t>
+          <t>visit_date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Triglycerides, week 12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NCIT:C64812 (Triglycerides)</t>
+          <t>ISO-8601 date</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4246,103 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Protocol adherence</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0-100</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>% (0-100)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>adverse_event</t>
+          <t>investigator_orcid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Any adverse event reported</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>ORCID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes | no</t>
+          <t>0000-0002-1825-0097</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NCIT:C41331 (Adverse Event)</t>
+          <t>ORCID identifier (https://orcid.org/)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>withdrew</t>
+          <t>reference_pmid</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Withdrew before week 12</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>PubMed ID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes | no</t>
+          <t>31813466</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NCIT:C49634 (Withdrawal)</t>
+          <t>PubMed identifier (https://pubmed.ncbi.nlm.nih.gov/)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>collection_date</t>
+          <t>protocol_doi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Final visit date</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ISO-8601</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10.5281/zenodo.0000000</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NCIT:C81286 (Date)</t>
+          <t>DOI (https://doi.org/)</t>
         </is>
       </c>
     </row>
